--- a/Config/Excels/__beans__.xlsx
+++ b/Config/Excels/__beans__.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -165,127 +165,16 @@
     <t>对应资源的文件名</t>
   </si>
   <si>
-    <t>ShowPositionAndResId</t>
-  </si>
-  <si>
-    <t>多立绘展示</t>
-  </si>
-  <si>
-    <t>用于设置多立绘的位置和资源获取</t>
-  </si>
-  <si>
-    <t>painting_postion</t>
-  </si>
-  <si>
-    <t>res.ShowPostion</t>
-  </si>
-  <si>
-    <t>立绘位置</t>
-  </si>
-  <si>
-    <t>res_id</t>
-  </si>
-  <si>
-    <t>资源ID</t>
-  </si>
-  <si>
-    <t>StoryCondition</t>
-  </si>
-  <si>
-    <t>用于设置剧情的前置条件配置</t>
-  </si>
-  <si>
-    <t>StoryId</t>
-  </si>
-  <si>
-    <t>剧情ID</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>story.ConditionType</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>(list#sep=|),int</t>
-  </si>
-  <si>
-    <t>条件</t>
-  </si>
-  <si>
-    <t>VideoTextSubtitles</t>
-  </si>
-  <si>
-    <t>视频字幕</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>时间</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>字幕内容</t>
-  </si>
-  <si>
-    <t>LLKLayout</t>
-  </si>
-  <si>
-    <t>连连看行列参数</t>
-  </si>
-  <si>
-    <t>col</t>
-  </si>
-  <si>
-    <t>列</t>
-  </si>
-  <si>
-    <t>row</t>
-  </si>
-  <si>
-    <t>行</t>
-  </si>
-  <si>
-    <t>TimerParams</t>
-  </si>
-  <si>
-    <t>时间挑战参数</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>难度级别</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>天选值</t>
-  </si>
-  <si>
     <t>CmdArgs</t>
   </si>
   <si>
     <t>命令参数</t>
   </si>
   <si>
-    <t>cmd</t>
-  </si>
-  <si>
     <t>CmdType</t>
   </si>
   <si>
-    <t>Args</t>
+    <t>args</t>
   </si>
   <si>
     <t>array,string</t>
@@ -454,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,24 +382,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -684,7 +561,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -705,19 +582,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -844,7 +708,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -856,119 +720,119 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1009,30 +873,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1047,14 +893,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1115,6 +955,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1375,7 +1222,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="22.6666666666667" customWidth="1"/>
@@ -1419,15 +1266,15 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
@@ -1444,7 +1291,7 @@
       <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="16" t="s">
         <v>5</v>
       </c>
       <c r="L2" t="s">
@@ -1459,7 +1306,7 @@
       <c r="O2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="P2" s="16" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1484,7 +1331,7 @@
       <c r="J3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="16" t="s">
         <v>18</v>
       </c>
       <c r="L3" t="s">
@@ -1496,7 +1343,7 @@
       <c r="N3" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1521,7 +1368,7 @@
         <v>26</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="23" t="s">
+      <c r="L4" s="17" t="s">
         <v>27</v>
       </c>
       <c r="M4" s="5"/>
@@ -1542,7 +1389,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="17" t="s">
         <v>27</v>
       </c>
       <c r="M5" s="5"/>
@@ -1569,7 +1416,7 @@
         <v>34</v>
       </c>
       <c r="K6" s="8"/>
-      <c r="L6" s="24" t="s">
+      <c r="L6" s="18" t="s">
         <v>35</v>
       </c>
       <c r="M6" s="8"/>
@@ -1590,7 +1437,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="8"/>
-      <c r="L7" s="24" t="s">
+      <c r="L7" s="18" t="s">
         <v>35</v>
       </c>
       <c r="M7" s="8"/>
@@ -1617,7 +1464,7 @@
         <v>34</v>
       </c>
       <c r="K8" s="11"/>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="19" t="s">
         <v>35</v>
       </c>
       <c r="M8" s="11"/>
@@ -1638,7 +1485,7 @@
         <v>43</v>
       </c>
       <c r="K9" s="11"/>
-      <c r="L9" s="25" t="s">
+      <c r="L9" s="19" t="s">
         <v>35</v>
       </c>
       <c r="M9" s="11"/>
@@ -1646,304 +1493,51 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" ht="25" customHeight="1" spans="2:14">
       <c r="B10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13" t="s">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13" t="s">
-        <v>50</v>
-      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="13"/>
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13" t="s">
-        <v>52</v>
-      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="14"/>
+      <c r="N11" s="13"/>
     </row>
-    <row r="12" spans="2:14">
-      <c r="B12" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="B15" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="M16" s="17"/>
-      <c r="N16" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
-      <c r="B17" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="19"/>
-      <c r="N17" s="18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18" s="10"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="K18" s="20"/>
-      <c r="L18" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="20"/>
-      <c r="N18" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1" spans="2:14">
-      <c r="B19" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="20"/>
-      <c r="N19" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="K20" s="19"/>
-      <c r="L20" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="M20" s="19"/>
-      <c r="N20" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="2:14">
-      <c r="B21" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="18"/>
-    </row>
-    <row r="22" spans="2:14">
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="18"/>
-    </row>
-    <row r="24" ht="25" customHeight="1"/>
+    <row r="13" ht="25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/Config/Excels/__beans__.xlsx
+++ b/Config/Excels/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -93,91 +93,6 @@
   </si>
   <si>
     <t>字段变体</t>
-  </si>
-  <si>
-    <t>RangeTowNumber</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>范围</t>
-  </si>
-  <si>
-    <t>取两个值的范围:
-1,3 就相当于[1,3)</t>
-  </si>
-  <si>
-    <t>range_1</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>范围1</t>
-  </si>
-  <si>
-    <t>range_2</t>
-  </si>
-  <si>
-    <t>范围2</t>
-  </si>
-  <si>
-    <t>TranslateCKBean</t>
-  </si>
-  <si>
-    <t>翻译Name Key对象</t>
-  </si>
-  <si>
-    <t>用于保存中文原content以及对应的国际化Key</t>
-  </si>
-  <si>
-    <t>content</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>对应Key</t>
-  </si>
-  <si>
-    <t>ResourceCKBean</t>
-  </si>
-  <si>
-    <t>资源Name Filename对象</t>
-  </si>
-  <si>
-    <t>用于资源在游戏内的名字展示,以及资源在目录下的资产名称</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>file_name</t>
-  </si>
-  <si>
-    <t>对应资源的文件名</t>
-  </si>
-  <si>
-    <t>CmdArgs</t>
-  </si>
-  <si>
-    <t>命令参数</t>
-  </si>
-  <si>
-    <t>CmdType</t>
-  </si>
-  <si>
-    <t>args</t>
-  </si>
-  <si>
-    <t>array,string</t>
   </si>
 </sst>
 </file>
@@ -343,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,157 +279,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -708,7 +605,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -732,16 +629,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -750,13 +647,25 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -807,32 +716,20 @@
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -845,56 +742,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -955,13 +807,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1222,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="22.6666666666667" customWidth="1"/>
     <col min="3" max="3" width="20.6333333333333" customWidth="1"/>
@@ -1266,15 +1111,15 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
@@ -1291,7 +1136,7 @@
       <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="L2" t="s">
@@ -1306,7 +1151,7 @@
       <c r="O2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1331,7 +1176,7 @@
       <c r="J3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="5" t="s">
         <v>18</v>
       </c>
       <c r="L3" t="s">
@@ -1343,201 +1188,11 @@
       <c r="N3" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="P3" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="2:14">
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14">
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5" spans="2:14">
-      <c r="B6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14">
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="2:14">
-      <c r="B8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14">
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1" spans="2:14">
-      <c r="B10" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="13"/>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" s="14"/>
-      <c r="N11" s="13"/>
-    </row>
-    <row r="13" ht="25" customHeight="1"/>
+    <row r="5" ht="25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
